--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/AUSTRALIA-MATARANKA_Datenbank/after_conversion_australia_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/AUSTRALIA-MATARANKA_Datenbank/after_conversion_australia_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="111">
   <si>
     <t>location</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>Database_number</t>
+  </si>
+  <si>
+    <t>Database_name</t>
   </si>
   <si>
     <t>Daly</t>
@@ -707,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD85"/>
+  <dimension ref="A1:AE85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -734,9 +737,10 @@
     <col min="28" max="28" width="18.7109375" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" customWidth="1"/>
     <col min="30" max="30" width="17.7109375" customWidth="1"/>
+    <col min="31" max="31" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -827,13 +831,16 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:30">
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2">
         <v>-14.444255748</v>
@@ -869,12 +876,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3">
         <v>-14.54653</v>
@@ -910,12 +917,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4">
         <v>-14.710453</v>
@@ -951,12 +958,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C5">
         <v>-14.710453</v>
@@ -989,12 +996,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6">
         <v>-14.57557</v>
@@ -1030,12 +1037,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7">
         <v>-14.48369</v>
@@ -1071,12 +1078,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8">
         <v>-14.457564171</v>
@@ -1112,12 +1119,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:31">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9">
         <v>-14.5679</v>
@@ -1153,12 +1160,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:31">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10">
         <v>-14.454347743</v>
@@ -1194,12 +1201,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11">
         <v>-14.41105</v>
@@ -1232,12 +1239,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:31">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12">
         <v>-14.50392779</v>
@@ -1273,12 +1280,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:31">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13">
         <v>-14.50392779</v>
@@ -1311,12 +1318,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:31">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C14">
         <v>-14.488736</v>
@@ -1352,12 +1359,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:31">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15">
         <v>-14.383915</v>
@@ -1393,12 +1400,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:31">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16">
         <v>-14.47812</v>
@@ -1436,10 +1443,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17">
         <v>-14.45767</v>
@@ -1477,10 +1484,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C18">
         <v>-14.47144</v>
@@ -1518,10 +1525,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C19">
         <v>-14.47399</v>
@@ -1559,10 +1566,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C20">
         <v>-14.44705</v>
@@ -1600,10 +1607,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21">
         <v>-14.4563</v>
@@ -1641,10 +1648,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C22">
         <v>-14.48668</v>
@@ -1682,10 +1689,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C23">
         <v>-14.4449</v>
@@ -1723,10 +1730,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C24">
         <v>-14.45287</v>
@@ -1764,10 +1771,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C25">
         <v>-14.46378</v>
@@ -1805,10 +1812,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C26">
         <v>-14.48027</v>
@@ -1846,10 +1853,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C27">
         <v>-14.46632</v>
@@ -1887,10 +1894,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C28">
         <v>-14.49033</v>
@@ -1928,10 +1935,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C29">
         <v>-14.46596</v>
@@ -1969,10 +1976,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C30">
         <v>-14.539374</v>
@@ -2010,10 +2017,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C31">
         <v>-14.46924</v>
@@ -2051,10 +2058,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C32">
         <v>-14.47091</v>
@@ -2092,10 +2099,10 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C33">
         <v>-14.477963</v>
@@ -2133,10 +2140,10 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C34">
         <v>-14.38877</v>
@@ -2174,10 +2181,10 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C35">
         <v>-14.38877</v>
@@ -2215,10 +2222,10 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C36">
         <v>-14.47217</v>
@@ -2256,10 +2263,10 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C37">
         <v>-14.45491</v>
@@ -2276,10 +2283,10 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C38">
         <v>-14.51583</v>
@@ -2317,10 +2324,10 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C39">
         <v>-14.48099</v>
@@ -2358,10 +2365,10 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B40" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C40">
         <v>-14.46388</v>
@@ -2399,10 +2406,10 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C41">
         <v>-14.6484038311049</v>
@@ -2440,10 +2447,10 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B42" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C42">
         <v>-14.5597609146966</v>
@@ -2481,10 +2488,10 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C43">
         <v>-14.43828</v>
@@ -2522,10 +2529,10 @@
     </row>
     <row r="44" spans="1:30">
       <c r="A44" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C44">
         <v>-14.48024</v>
@@ -2563,10 +2570,10 @@
     </row>
     <row r="45" spans="1:30">
       <c r="A45" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B45" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C45">
         <v>-14.47885</v>
@@ -2604,10 +2611,10 @@
     </row>
     <row r="46" spans="1:30">
       <c r="A46" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B46" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C46">
         <v>-14.46072</v>
@@ -2645,10 +2652,10 @@
     </row>
     <row r="47" spans="1:30">
       <c r="A47" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C47">
         <v>-14.37364</v>
@@ -2686,10 +2693,10 @@
     </row>
     <row r="48" spans="1:30">
       <c r="A48" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B48" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C48">
         <v>-14.6052</v>
@@ -2727,10 +2734,10 @@
     </row>
     <row r="49" spans="1:30">
       <c r="A49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C49">
         <v>-14.49207</v>
@@ -2768,10 +2775,10 @@
     </row>
     <row r="50" spans="1:30">
       <c r="A50" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B50" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C50">
         <v>-14.41238</v>
@@ -2809,10 +2816,10 @@
     </row>
     <row r="51" spans="1:30">
       <c r="A51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B51" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C51">
         <v>-14.449762341958</v>
@@ -2850,10 +2857,10 @@
     </row>
     <row r="52" spans="1:30">
       <c r="A52" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B52" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C52">
         <v>-14.57862</v>
@@ -2891,10 +2898,10 @@
     </row>
     <row r="53" spans="1:30">
       <c r="A53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B53" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C53">
         <v>-14.42845</v>
@@ -2932,10 +2939,10 @@
     </row>
     <row r="54" spans="1:30">
       <c r="A54" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C54">
         <v>-14.462216</v>
@@ -2973,10 +2980,10 @@
     </row>
     <row r="55" spans="1:30">
       <c r="A55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B55" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C55">
         <v>-14.5049570813794</v>
@@ -3014,10 +3021,10 @@
     </row>
     <row r="56" spans="1:30">
       <c r="A56" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B56" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C56">
         <v>-14.53955</v>
@@ -3055,10 +3062,10 @@
     </row>
     <row r="57" spans="1:30">
       <c r="A57" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B57" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C57">
         <v>-14.61845</v>
@@ -3096,10 +3103,10 @@
     </row>
     <row r="58" spans="1:30">
       <c r="A58" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B58" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C58">
         <v>-15.601</v>
@@ -3137,10 +3144,10 @@
     </row>
     <row r="59" spans="1:30">
       <c r="A59" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B59" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C59">
         <v>-16.4246274084702</v>
@@ -3178,10 +3185,10 @@
     </row>
     <row r="60" spans="1:30">
       <c r="A60" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B60" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C60">
         <v>-16.3854521742903</v>
@@ -3219,10 +3226,10 @@
     </row>
     <row r="61" spans="1:30">
       <c r="A61" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B61" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C61">
         <v>-16.3274</v>
@@ -3260,10 +3267,10 @@
     </row>
     <row r="62" spans="1:30">
       <c r="A62" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B62" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C62">
         <v>-16.4856</v>
@@ -3301,10 +3308,10 @@
     </row>
     <row r="63" spans="1:30">
       <c r="A63" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B63" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C63">
         <v>-16.9257</v>
@@ -3342,10 +3349,10 @@
     </row>
     <row r="64" spans="1:30">
       <c r="A64" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B64" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C64">
         <v>-16.5969</v>
@@ -3383,10 +3390,10 @@
     </row>
     <row r="65" spans="1:30">
       <c r="A65" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B65" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C65">
         <v>-16.3997</v>
@@ -3424,10 +3431,10 @@
     </row>
     <row r="66" spans="1:30">
       <c r="A66" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B66" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C66">
         <v>-16.4561883563999</v>
@@ -3465,10 +3472,10 @@
     </row>
     <row r="67" spans="1:30">
       <c r="A67" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B67" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C67">
         <v>-16.48</v>
@@ -3506,10 +3513,10 @@
     </row>
     <row r="68" spans="1:30">
       <c r="A68" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B68" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C68">
         <v>-16.3464763323004</v>
@@ -3547,10 +3554,10 @@
     </row>
     <row r="69" spans="1:30">
       <c r="A69" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B69" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C69">
         <v>-16.619857486</v>
@@ -3588,10 +3595,10 @@
     </row>
     <row r="70" spans="1:30">
       <c r="A70" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B70" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C70">
         <v>-16.5485</v>
@@ -3629,10 +3636,10 @@
     </row>
     <row r="71" spans="1:30">
       <c r="A71" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B71" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C71">
         <v>-17.0648</v>
@@ -3670,10 +3677,10 @@
     </row>
     <row r="72" spans="1:30">
       <c r="A72" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B72" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C72">
         <v>-18.323</v>
@@ -3711,10 +3718,10 @@
     </row>
     <row r="73" spans="1:30">
       <c r="A73" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B73" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C73">
         <v>-18.0408</v>
@@ -3752,10 +3759,10 @@
     </row>
     <row r="74" spans="1:30">
       <c r="A74" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B74" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C74">
         <v>-17.7401</v>
@@ -3793,10 +3800,10 @@
     </row>
     <row r="75" spans="1:30">
       <c r="A75" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B75" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C75">
         <v>-15.271023</v>
@@ -3834,10 +3841,10 @@
     </row>
     <row r="76" spans="1:30">
       <c r="A76" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B76" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C76">
         <v>-15.3733385942091</v>
@@ -3875,10 +3882,10 @@
     </row>
     <row r="77" spans="1:30">
       <c r="A77" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B77" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C77">
         <v>-15.5927</v>
@@ -3916,10 +3923,10 @@
     </row>
     <row r="78" spans="1:30">
       <c r="A78" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B78" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C78">
         <v>-15.86713284</v>
@@ -3957,10 +3964,10 @@
     </row>
     <row r="79" spans="1:30">
       <c r="A79" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B79" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C79">
         <v>-16.3464763323004</v>
@@ -3998,10 +4005,10 @@
     </row>
     <row r="80" spans="1:30">
       <c r="A80" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B80" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C80">
         <v>-16.308779</v>
@@ -4039,10 +4046,10 @@
     </row>
     <row r="81" spans="1:30">
       <c r="A81" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B81" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C81">
         <v>-16.43265831</v>
@@ -4080,10 +4087,10 @@
     </row>
     <row r="82" spans="1:30">
       <c r="A82" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B82" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C82">
         <v>-16.38771649</v>
@@ -4121,7 +4128,7 @@
     </row>
     <row r="83" spans="1:30">
       <c r="B83" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C83">
         <v>-14.933136</v>
@@ -4159,7 +4166,7 @@
     </row>
     <row r="84" spans="1:30">
       <c r="B84" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C84">
         <v>-14.933136</v>
@@ -4197,7 +4204,7 @@
     </row>
     <row r="85" spans="1:30">
       <c r="B85" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C85">
         <v>-14.933136</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/AUSTRALIA-MATARANKA_Datenbank/after_conversion_australia_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/AUSTRALIA-MATARANKA_Datenbank/after_conversion_australia_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="112">
   <si>
     <t>location</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>Botany Walk Spring</t>
+  </si>
+  <si>
+    <t>Limestone</t>
   </si>
 </sst>
 </file>
@@ -848,6 +851,9 @@
       <c r="D2">
         <v>132.285449884</v>
       </c>
+      <c r="F2" t="s">
+        <v>111</v>
+      </c>
       <c r="L2">
         <v>13.62219065606568</v>
       </c>
@@ -889,6 +895,9 @@
       <c r="D3">
         <v>132.395</v>
       </c>
+      <c r="F3" t="s">
+        <v>111</v>
+      </c>
       <c r="L3">
         <v>11.68435723631512</v>
       </c>
@@ -930,6 +939,9 @@
       <c r="D4">
         <v>132.059519</v>
       </c>
+      <c r="F4" t="s">
+        <v>111</v>
+      </c>
       <c r="L4">
         <v>11.30960240625839</v>
       </c>
@@ -971,6 +983,9 @@
       <c r="D5">
         <v>132.059519</v>
       </c>
+      <c r="F5" t="s">
+        <v>111</v>
+      </c>
       <c r="L5">
         <v>8.397280418038347</v>
       </c>
@@ -1009,6 +1024,9 @@
       <c r="D6">
         <v>132.4713</v>
       </c>
+      <c r="F6" t="s">
+        <v>111</v>
+      </c>
       <c r="L6">
         <v>12.55895144364739</v>
       </c>
@@ -1050,6 +1068,9 @@
       <c r="D7">
         <v>132.247</v>
       </c>
+      <c r="F7" t="s">
+        <v>111</v>
+      </c>
       <c r="L7">
         <v>12.69596416485628</v>
       </c>
@@ -1091,6 +1112,9 @@
       <c r="D8">
         <v>132.2414534</v>
       </c>
+      <c r="F8" t="s">
+        <v>111</v>
+      </c>
       <c r="L8">
         <v>9.408459770299713</v>
       </c>
@@ -1132,6 +1156,9 @@
       <c r="D9">
         <v>132.5053</v>
       </c>
+      <c r="F9" t="s">
+        <v>111</v>
+      </c>
       <c r="L9">
         <v>10.28869814191514</v>
       </c>
@@ -1173,6 +1200,9 @@
       <c r="D10">
         <v>132.213009476</v>
       </c>
+      <c r="F10" t="s">
+        <v>111</v>
+      </c>
       <c r="L10">
         <v>10.74289602046917</v>
       </c>
@@ -1214,6 +1244,9 @@
       <c r="D11">
         <v>132.2043</v>
       </c>
+      <c r="F11" t="s">
+        <v>111</v>
+      </c>
       <c r="L11">
         <v>7.580231761410245</v>
       </c>
@@ -1252,6 +1285,9 @@
       <c r="D12">
         <v>132.295794198</v>
       </c>
+      <c r="F12" t="s">
+        <v>111</v>
+      </c>
       <c r="L12">
         <v>11.7869315143053</v>
       </c>
@@ -1293,6 +1329,9 @@
       <c r="D13">
         <v>132.295794198</v>
       </c>
+      <c r="F13" t="s">
+        <v>111</v>
+      </c>
       <c r="L13">
         <v>8.956370599401328</v>
       </c>
@@ -1331,6 +1370,9 @@
       <c r="D14">
         <v>132.255447</v>
       </c>
+      <c r="F14" t="s">
+        <v>111</v>
+      </c>
       <c r="L14">
         <v>10.76122587505537</v>
       </c>
@@ -1372,6 +1414,9 @@
       <c r="D15">
         <v>132.150887</v>
       </c>
+      <c r="F15" t="s">
+        <v>111</v>
+      </c>
       <c r="L15">
         <v>12.2689407967535</v>
       </c>
@@ -1413,6 +1458,9 @@
       <c r="D16">
         <v>132.2691</v>
       </c>
+      <c r="F16" t="s">
+        <v>111</v>
+      </c>
       <c r="L16">
         <v>6.886815702847746</v>
       </c>
@@ -1454,6 +1502,9 @@
       <c r="D17">
         <v>132.2564</v>
       </c>
+      <c r="F17" t="s">
+        <v>111</v>
+      </c>
       <c r="L17">
         <v>11.63019322950011</v>
       </c>
@@ -1495,6 +1546,9 @@
       <c r="D18">
         <v>132.235</v>
       </c>
+      <c r="F18" t="s">
+        <v>111</v>
+      </c>
       <c r="L18">
         <v>10.7643187003566</v>
       </c>
@@ -1536,6 +1590,9 @@
       <c r="D19">
         <v>132.2368</v>
       </c>
+      <c r="F19" t="s">
+        <v>111</v>
+      </c>
       <c r="L19">
         <v>10.7998263033176</v>
       </c>
@@ -1577,6 +1634,9 @@
       <c r="D20">
         <v>132.2492</v>
       </c>
+      <c r="F20" t="s">
+        <v>111</v>
+      </c>
       <c r="L20">
         <v>11.66787734408918</v>
       </c>
@@ -1618,6 +1678,9 @@
       <c r="D21">
         <v>132.261</v>
       </c>
+      <c r="F21" t="s">
+        <v>111</v>
+      </c>
       <c r="L21">
         <v>13.98091054030656</v>
       </c>
@@ -1659,6 +1722,9 @@
       <c r="D22">
         <v>132.2505</v>
       </c>
+      <c r="F22" t="s">
+        <v>111</v>
+      </c>
       <c r="L22">
         <v>11.98764830701136</v>
       </c>
@@ -1700,6 +1766,9 @@
       <c r="D23">
         <v>132.2504</v>
       </c>
+      <c r="F23" t="s">
+        <v>111</v>
+      </c>
       <c r="L23">
         <v>12.79407680808057</v>
       </c>
@@ -1741,6 +1810,9 @@
       <c r="D24">
         <v>132.2453</v>
       </c>
+      <c r="F24" t="s">
+        <v>111</v>
+      </c>
       <c r="L24">
         <v>11.94444921053599</v>
       </c>
@@ -1782,6 +1854,9 @@
       <c r="D25">
         <v>132.2365</v>
       </c>
+      <c r="F25" t="s">
+        <v>111</v>
+      </c>
       <c r="L25">
         <v>9.863211301696008</v>
       </c>
@@ -1823,6 +1898,9 @@
       <c r="D26">
         <v>132.2401</v>
       </c>
+      <c r="F26" t="s">
+        <v>111</v>
+      </c>
       <c r="L26">
         <v>13.10219749940356</v>
       </c>
@@ -1864,6 +1942,9 @@
       <c r="D27">
         <v>132.2837</v>
       </c>
+      <c r="F27" t="s">
+        <v>111</v>
+      </c>
       <c r="L27">
         <v>12.43018473208868</v>
       </c>
@@ -1905,6 +1986,9 @@
       <c r="D28">
         <v>132.2358</v>
       </c>
+      <c r="F28" t="s">
+        <v>111</v>
+      </c>
       <c r="L28">
         <v>12.28126812420775</v>
       </c>
@@ -1946,6 +2030,9 @@
       <c r="D29">
         <v>132.284</v>
       </c>
+      <c r="F29" t="s">
+        <v>111</v>
+      </c>
       <c r="L29">
         <v>10.59587298929881</v>
       </c>
@@ -1987,6 +2074,9 @@
       <c r="D30">
         <v>132.174356</v>
       </c>
+      <c r="F30" t="s">
+        <v>111</v>
+      </c>
       <c r="L30">
         <v>9.747854674443804</v>
       </c>
@@ -2028,6 +2118,9 @@
       <c r="D31">
         <v>132.1967</v>
       </c>
+      <c r="F31" t="s">
+        <v>111</v>
+      </c>
       <c r="L31">
         <v>10.09798361241654</v>
       </c>
@@ -2069,6 +2162,9 @@
       <c r="D32">
         <v>132.2283</v>
       </c>
+      <c r="F32" t="s">
+        <v>111</v>
+      </c>
       <c r="L32">
         <v>11.51300587536608</v>
       </c>
@@ -2110,6 +2206,9 @@
       <c r="D33">
         <v>132.457248</v>
       </c>
+      <c r="F33" t="s">
+        <v>111</v>
+      </c>
       <c r="L33">
         <v>12.70884383652736</v>
       </c>
@@ -2151,6 +2250,9 @@
       <c r="D34">
         <v>132.148</v>
       </c>
+      <c r="F34" t="s">
+        <v>111</v>
+      </c>
       <c r="L34">
         <v>11.81033445749737</v>
       </c>
@@ -2192,6 +2294,9 @@
       <c r="D35">
         <v>132.148</v>
       </c>
+      <c r="F35" t="s">
+        <v>111</v>
+      </c>
       <c r="L35">
         <v>10.39765096445285</v>
       </c>
@@ -2233,6 +2338,9 @@
       <c r="D36">
         <v>132.2196</v>
       </c>
+      <c r="F36" t="s">
+        <v>111</v>
+      </c>
       <c r="L36">
         <v>11.29765751979151</v>
       </c>
@@ -2274,6 +2382,9 @@
       <c r="D37">
         <v>132.2581</v>
       </c>
+      <c r="F37" t="s">
+        <v>111</v>
+      </c>
       <c r="L37">
         <v>0</v>
       </c>
@@ -2294,6 +2405,9 @@
       <c r="D38">
         <v>132.4334</v>
       </c>
+      <c r="F38" t="s">
+        <v>111</v>
+      </c>
       <c r="L38">
         <v>11.40827096091096</v>
       </c>
@@ -2335,6 +2449,9 @@
       <c r="D39">
         <v>132.2252</v>
       </c>
+      <c r="F39" t="s">
+        <v>111</v>
+      </c>
       <c r="L39">
         <v>12.72052626875368</v>
       </c>
@@ -2376,6 +2493,9 @@
       <c r="D40">
         <v>132.2605</v>
       </c>
+      <c r="F40" t="s">
+        <v>111</v>
+      </c>
       <c r="L40">
         <v>12.07657571770761</v>
       </c>
@@ -2417,6 +2537,9 @@
       <c r="D41">
         <v>132.013681706129</v>
       </c>
+      <c r="F41" t="s">
+        <v>111</v>
+      </c>
       <c r="L41">
         <v>11.94752133255534</v>
       </c>
@@ -2458,6 +2581,9 @@
       <c r="D42">
         <v>131.974755158304</v>
       </c>
+      <c r="F42" t="s">
+        <v>111</v>
+      </c>
       <c r="L42">
         <v>12.2240383056948</v>
       </c>
@@ -2499,6 +2625,9 @@
       <c r="D43">
         <v>132.226</v>
       </c>
+      <c r="F43" t="s">
+        <v>111</v>
+      </c>
       <c r="L43">
         <v>12.40788093303927</v>
       </c>
@@ -2540,6 +2669,9 @@
       <c r="D44">
         <v>132.2559</v>
       </c>
+      <c r="F44" t="s">
+        <v>111</v>
+      </c>
       <c r="L44">
         <v>11.59067498784076</v>
       </c>
@@ -2581,6 +2713,9 @@
       <c r="D45">
         <v>132.2347</v>
       </c>
+      <c r="F45" t="s">
+        <v>111</v>
+      </c>
       <c r="L45">
         <v>11.23016671181484</v>
       </c>
@@ -2622,6 +2757,9 @@
       <c r="D46">
         <v>132.3954</v>
       </c>
+      <c r="F46" t="s">
+        <v>111</v>
+      </c>
       <c r="L46">
         <v>14.21499342574302</v>
       </c>
@@ -2663,6 +2801,9 @@
       <c r="D47">
         <v>132.1554</v>
       </c>
+      <c r="F47" t="s">
+        <v>111</v>
+      </c>
       <c r="L47">
         <v>13.05783139686371</v>
       </c>
@@ -2704,6 +2845,9 @@
       <c r="D48">
         <v>132.4477</v>
       </c>
+      <c r="F48" t="s">
+        <v>111</v>
+      </c>
       <c r="L48">
         <v>12.34968930957336</v>
       </c>
@@ -2745,6 +2889,9 @@
       <c r="D49">
         <v>132.331</v>
       </c>
+      <c r="F49" t="s">
+        <v>111</v>
+      </c>
       <c r="L49">
         <v>13.02908076222307</v>
       </c>
@@ -2786,6 +2933,9 @@
       <c r="D50">
         <v>132.1743</v>
       </c>
+      <c r="F50" t="s">
+        <v>111</v>
+      </c>
       <c r="L50">
         <v>11.76262192344071</v>
       </c>
@@ -2827,6 +2977,9 @@
       <c r="D51">
         <v>131.688069705176</v>
       </c>
+      <c r="F51" t="s">
+        <v>111</v>
+      </c>
       <c r="L51">
         <v>10.40668230640246</v>
       </c>
@@ -2868,6 +3021,9 @@
       <c r="D52">
         <v>132.5077</v>
       </c>
+      <c r="F52" t="s">
+        <v>111</v>
+      </c>
       <c r="L52">
         <v>11.28055549191623</v>
       </c>
@@ -2909,6 +3065,9 @@
       <c r="D53">
         <v>132.2083</v>
       </c>
+      <c r="F53" t="s">
+        <v>111</v>
+      </c>
       <c r="L53">
         <v>10.92452699790378</v>
       </c>
@@ -2950,6 +3109,9 @@
       <c r="D54">
         <v>132.310862</v>
       </c>
+      <c r="F54" t="s">
+        <v>111</v>
+      </c>
       <c r="L54">
         <v>11.79981262171423</v>
       </c>
@@ -2991,6 +3153,9 @@
       <c r="D55">
         <v>131.71128322119</v>
       </c>
+      <c r="F55" t="s">
+        <v>111</v>
+      </c>
       <c r="L55">
         <v>7.414733217399847</v>
       </c>
@@ -3032,6 +3197,9 @@
       <c r="D56">
         <v>132.4678</v>
       </c>
+      <c r="F56" t="s">
+        <v>111</v>
+      </c>
       <c r="L56">
         <v>9.466283097315891</v>
       </c>
@@ -3072,6 +3240,9 @@
       </c>
       <c r="D57">
         <v>132.2018</v>
+      </c>
+      <c r="F57" t="s">
+        <v>111</v>
       </c>
       <c r="L57">
         <v>10.41153861203384</v>
@@ -3114,6 +3285,9 @@
       <c r="D58">
         <v>133.1775</v>
       </c>
+      <c r="F58" t="s">
+        <v>111</v>
+      </c>
       <c r="L58">
         <v>32.69740900392016</v>
       </c>
@@ -3155,6 +3329,9 @@
       <c r="D59">
         <v>134.602017398501</v>
       </c>
+      <c r="F59" t="s">
+        <v>111</v>
+      </c>
       <c r="L59">
         <v>20.75703711186543</v>
       </c>
@@ -3196,6 +3373,9 @@
       <c r="D60">
         <v>134.633512797705</v>
       </c>
+      <c r="F60" t="s">
+        <v>111</v>
+      </c>
       <c r="L60">
         <v>24.07546627006172</v>
       </c>
@@ -3237,6 +3417,9 @@
       <c r="D61">
         <v>134.7119</v>
       </c>
+      <c r="F61" t="s">
+        <v>111</v>
+      </c>
       <c r="L61">
         <v>34.82061443693325</v>
       </c>
@@ -3278,6 +3461,9 @@
       <c r="D62">
         <v>134.7261</v>
       </c>
+      <c r="F62" t="s">
+        <v>111</v>
+      </c>
       <c r="L62">
         <v>25.29957684750493</v>
       </c>
@@ -3319,6 +3505,9 @@
       <c r="D63">
         <v>134.7913</v>
       </c>
+      <c r="F63" t="s">
+        <v>111</v>
+      </c>
       <c r="L63">
         <v>24.16081789342578</v>
       </c>
@@ -3360,6 +3549,9 @@
       <c r="D64">
         <v>134.8011</v>
       </c>
+      <c r="F64" t="s">
+        <v>111</v>
+      </c>
       <c r="L64">
         <v>29.18148107037641</v>
       </c>
@@ -3401,6 +3593,9 @@
       <c r="D65">
         <v>134.7048</v>
       </c>
+      <c r="F65" t="s">
+        <v>111</v>
+      </c>
       <c r="L65">
         <v>25.80030421587406</v>
       </c>
@@ -3442,6 +3637,9 @@
       <c r="D66">
         <v>134.648044388353</v>
       </c>
+      <c r="F66" t="s">
+        <v>111</v>
+      </c>
       <c r="L66">
         <v>24.05744616112396</v>
       </c>
@@ -3483,6 +3681,9 @@
       <c r="D67">
         <v>133.9798</v>
       </c>
+      <c r="F67" t="s">
+        <v>111</v>
+      </c>
       <c r="L67">
         <v>23.34653231236302</v>
       </c>
@@ -3524,6 +3725,9 @@
       <c r="D68">
         <v>133.884561881875</v>
       </c>
+      <c r="F68" t="s">
+        <v>111</v>
+      </c>
       <c r="L68">
         <v>21.52860716656957</v>
       </c>
@@ -3565,6 +3769,9 @@
       <c r="D69">
         <v>133.578681781</v>
       </c>
+      <c r="F69" t="s">
+        <v>111</v>
+      </c>
       <c r="L69">
         <v>21.87930345666272</v>
       </c>
@@ -3606,6 +3813,9 @@
       <c r="D70">
         <v>133.7701</v>
       </c>
+      <c r="F70" t="s">
+        <v>111</v>
+      </c>
       <c r="L70">
         <v>22.29245736483353</v>
       </c>
@@ -3647,6 +3857,9 @@
       <c r="D71">
         <v>133.41</v>
       </c>
+      <c r="F71" t="s">
+        <v>111</v>
+      </c>
       <c r="L71">
         <v>30.77405969624247</v>
       </c>
@@ -3688,6 +3901,9 @@
       <c r="D72">
         <v>133.8874</v>
       </c>
+      <c r="F72" t="s">
+        <v>111</v>
+      </c>
       <c r="L72">
         <v>22.43022766261104</v>
       </c>
@@ -3729,6 +3945,9 @@
       <c r="D73">
         <v>134.3971</v>
       </c>
+      <c r="F73" t="s">
+        <v>111</v>
+      </c>
       <c r="L73">
         <v>40.49492717798341</v>
       </c>
@@ -3770,6 +3989,9 @@
       <c r="D74">
         <v>133.724909</v>
       </c>
+      <c r="F74" t="s">
+        <v>111</v>
+      </c>
       <c r="L74">
         <v>28.21578652742604</v>
       </c>
@@ -3811,6 +4033,9 @@
       <c r="D75">
         <v>133.125561</v>
       </c>
+      <c r="F75" t="s">
+        <v>111</v>
+      </c>
       <c r="L75">
         <v>34.9275098407493</v>
       </c>
@@ -3852,6 +4077,9 @@
       <c r="D76">
         <v>133.16522788068</v>
       </c>
+      <c r="F76" t="s">
+        <v>111</v>
+      </c>
       <c r="L76">
         <v>29.96568748403686</v>
       </c>
@@ -3893,6 +4121,9 @@
       <c r="D77">
         <v>133.2249</v>
       </c>
+      <c r="F77" t="s">
+        <v>111</v>
+      </c>
       <c r="L77">
         <v>30.38439308685597</v>
       </c>
@@ -3934,6 +4165,9 @@
       <c r="D78">
         <v>133.4067349</v>
       </c>
+      <c r="F78" t="s">
+        <v>111</v>
+      </c>
       <c r="L78">
         <v>42.2947438444724</v>
       </c>
@@ -3975,6 +4209,9 @@
       <c r="D79">
         <v>133.884561881875</v>
       </c>
+      <c r="F79" t="s">
+        <v>111</v>
+      </c>
       <c r="L79">
         <v>21.57938290704912</v>
       </c>
@@ -4016,6 +4253,9 @@
       <c r="D80">
         <v>133.385114</v>
       </c>
+      <c r="F80" t="s">
+        <v>111</v>
+      </c>
       <c r="L80">
         <v>41.91785749390625</v>
       </c>
@@ -4057,6 +4297,9 @@
       <c r="D81">
         <v>134.5835343</v>
       </c>
+      <c r="F81" t="s">
+        <v>111</v>
+      </c>
       <c r="L81">
         <v>23.08770546009024</v>
       </c>
@@ -4098,6 +4341,9 @@
       <c r="D82">
         <v>134.7943708</v>
       </c>
+      <c r="F82" t="s">
+        <v>111</v>
+      </c>
       <c r="L82">
         <v>23.79806465974833</v>
       </c>
@@ -4136,6 +4382,9 @@
       <c r="D83">
         <v>133.134522</v>
       </c>
+      <c r="F83" t="s">
+        <v>111</v>
+      </c>
       <c r="L83">
         <v>72.93621004316877</v>
       </c>
@@ -4174,6 +4423,9 @@
       <c r="D84">
         <v>133.134522</v>
       </c>
+      <c r="F84" t="s">
+        <v>111</v>
+      </c>
       <c r="L84">
         <v>49.68780173349252</v>
       </c>
@@ -4211,6 +4463,9 @@
       </c>
       <c r="D85">
         <v>133.134522</v>
+      </c>
+      <c r="F85" t="s">
+        <v>111</v>
       </c>
       <c r="L85">
         <v>56.89226439096257</v>
